--- a/performance-dashboard/archive/交易表现_20260112.xlsx
+++ b/performance-dashboard/archive/交易表现_20260112.xlsx
@@ -531,26 +531,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,019,638.10</t>
+          <t>¥1,024,948.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+19,638.10</t>
+          <t>¥+24,948.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+35.84%</t>
+          <t>+44.09%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.648</v>
+        <v>5.605</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,24 +559,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1306%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6.6552%</t>
+          <t>6.6161%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -607,26 +607,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,042,439.98</t>
+          <t>¥1,049,943.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+42,439.98</t>
+          <t>¥+49,943.89</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.24%</t>
+          <t>+4.99%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+92.44%</t>
+          <t>+105.95%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.638</v>
+        <v>7.444</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,24 +635,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2796%</t>
+          <t>0.3071%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10.3159%</t>
+          <t>10.1306%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -683,26 +683,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,014,809.18</t>
+          <t>¥1,020,348.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+14,809.18</t>
+          <t>¥+20,348.80</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+26.05%</t>
+          <t>+34.80%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.431</v>
+        <v>5.661</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -711,24 +711,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0986%</t>
+          <t>0.1265%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.1597%</t>
+          <t>5.2833%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -759,26 +759,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,003,464.49</t>
+          <t>¥1,004,906.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+3,464.49</t>
+          <t>¥+4,906.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.60%</t>
+          <t>+7.52%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.575</v>
+        <v>2.382</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -787,24 +787,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0232%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.4506%</t>
+          <t>2.4176%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -835,26 +835,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,001,518.00</t>
+          <t>¥1,004,115.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+1,518.00</t>
+          <t>¥+4,115.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.42%</t>
+          <t>+6.28%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.472</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -863,24 +863,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0101%</t>
+          <t>0.0257%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.2193%</t>
+          <t>1.5200%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -911,26 +911,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,040,563.19</t>
+          <t>¥1,045,139.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+40,563.19</t>
+          <t>¥+45,139.78</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+87.06%</t>
+          <t>+92.41%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8.300000000000001</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -939,24 +939,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.2667%</t>
+          <t>0.2775%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7.8577%</t>
+          <t>7.6372%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -987,26 +987,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,026,881.61</t>
+          <t>¥1,032,294.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+26,881.61</t>
+          <t>¥+32,294.79</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.69%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+51.86%</t>
+          <t>+60.18%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6.192</v>
+        <v>7.075</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1015,24 +1015,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.1779%</t>
+          <t>0.1998%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6.9223%</t>
+          <t>6.8355%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1063,26 +1063,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,030,262.17</t>
+          <t>¥1,035,821.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+30,262.17</t>
+          <t>¥+35,821.52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+59.93%</t>
+          <t>+68.49%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.98</v>
+        <v>7.859</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1999%</t>
+          <t>0.2211%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6.9331%</t>
+          <t>6.8387%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1139,26 +1139,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,052,440.53</t>
+          <t>¥1,059,434.88</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+52,440.53</t>
+          <t>¥+59,434.88</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.24%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+123.67%</t>
+          <t>+135.34%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.436</v>
+        <v>8.087</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1167,24 +1167,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.3439%</t>
+          <t>0.3639%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11.3886%</t>
+          <t>11.0956%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1215,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,002,594.00</t>
+          <t>¥1,004,915.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+2,594.00</t>
+          <t>¥+4,915.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+4.16%</t>
+          <t>+7.54%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.387</v>
+        <v>4.536</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1243,24 +1243,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.0173%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.9959%</t>
+          <t>1.2678%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥1,011,144.42</t>
+          <t>¥1,014,230.30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥+11,144.42</t>
+          <t>¥+14,230.30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+19.07%</t>
+          <t>+23.30%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.44</v>
+        <v>4.249</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1319,24 +1319,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.0744%</t>
+          <t>0.0888%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.8735%</t>
+          <t>4.8014%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1367,26 +1367,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥1,042,601.48</t>
+          <t>¥1,049,086.38</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥+42,601.48</t>
+          <t>¥+49,086.38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+92.91%</t>
+          <t>+103.47%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.292</v>
+        <v>6.952</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.2809%</t>
+          <t>0.3022%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10.9356%</t>
+          <t>10.6692%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1443,26 +1443,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,007,811.62</t>
+          <t>¥1,011,061.62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+7,811.62</t>
+          <t>¥+11,061.62</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+13.04%</t>
+          <t>+17.71%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.849</v>
+        <v>5.152</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1471,24 +1471,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0521%</t>
+          <t>0.0690%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.8938%</t>
+          <t>2.9884%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1519,26 +1519,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥1,000,596.60</t>
+          <t>¥1,001,327.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥+596.60</t>
+          <t>¥+1,327.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-2.063</v>
+        <v>0.207</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1547,24 +1547,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.0040%</t>
+          <t>0.0083%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.4737%</t>
+          <t>0.5298%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1595,26 +1595,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥1,000,663.50</t>
+          <t>¥1,001,421.90</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥+663.50</t>
+          <t>¥+1,421.90</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-1.82</v>
+        <v>0.484</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.0044%</t>
+          <t>0.0089%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.4752%</t>
+          <t>0.5356%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1767,26 +1767,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,019,638.10</t>
+          <t>¥1,024,948.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+19,638.10</t>
+          <t>¥+24,948.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+35.84%</t>
+          <t>+44.09%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.648</v>
+        <v>5.605</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1795,24 +1795,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1306%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6.6552%</t>
+          <t>6.6161%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1843,26 +1843,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,042,439.98</t>
+          <t>¥1,049,943.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+42,439.98</t>
+          <t>¥+49,943.89</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.24%</t>
+          <t>+4.99%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+92.44%</t>
+          <t>+105.95%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.638</v>
+        <v>7.444</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1871,24 +1871,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2796%</t>
+          <t>0.3071%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10.3159%</t>
+          <t>10.1306%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1919,26 +1919,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,014,809.18</t>
+          <t>¥1,020,348.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+14,809.18</t>
+          <t>¥+20,348.80</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+26.05%</t>
+          <t>+34.80%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.431</v>
+        <v>5.661</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0986%</t>
+          <t>0.1265%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.1597%</t>
+          <t>5.2833%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1995,26 +1995,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,003,464.49</t>
+          <t>¥1,004,906.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+3,464.49</t>
+          <t>¥+4,906.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.60%</t>
+          <t>+7.52%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.575</v>
+        <v>2.382</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2023,24 +2023,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0232%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.4506%</t>
+          <t>2.4176%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,001,518.00</t>
+          <t>¥1,004,115.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+1,518.00</t>
+          <t>¥+4,115.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.42%</t>
+          <t>+6.28%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.472</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2099,24 +2099,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0101%</t>
+          <t>0.0257%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.2193%</t>
+          <t>1.5200%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2243,26 +2243,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,040,563.19</t>
+          <t>¥1,045,139.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+40,563.19</t>
+          <t>¥+45,139.78</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+87.06%</t>
+          <t>+92.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2271,24 +2271,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.2667%</t>
+          <t>0.2775%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.8577%</t>
+          <t>7.6372%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2319,26 +2319,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,026,881.61</t>
+          <t>¥1,032,294.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+26,881.61</t>
+          <t>¥+32,294.79</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.69%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+51.86%</t>
+          <t>+60.18%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.192</v>
+        <v>7.075</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2347,24 +2347,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1779%</t>
+          <t>0.1998%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6.9223%</t>
+          <t>6.8355%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2395,26 +2395,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,030,262.17</t>
+          <t>¥1,035,821.52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+30,262.17</t>
+          <t>¥+35,821.52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+59.93%</t>
+          <t>+68.49%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.98</v>
+        <v>7.859</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2423,24 +2423,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1999%</t>
+          <t>0.2211%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6.9331%</t>
+          <t>6.8387%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2471,26 +2471,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,052,440.53</t>
+          <t>¥1,059,434.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+52,440.53</t>
+          <t>¥+59,434.88</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.24%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+123.67%</t>
+          <t>+135.34%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.436</v>
+        <v>8.087</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2499,24 +2499,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.3439%</t>
+          <t>0.3639%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11.3886%</t>
+          <t>11.0956%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2547,26 +2547,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,002,594.00</t>
+          <t>¥1,004,915.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+2,594.00</t>
+          <t>¥+4,915.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+4.16%</t>
+          <t>+7.54%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.387</v>
+        <v>4.536</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2575,24 +2575,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0173%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9959%</t>
+          <t>1.2678%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2719,26 +2719,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,011,144.42</t>
+          <t>¥1,014,230.30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+11,144.42</t>
+          <t>¥+14,230.30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+19.07%</t>
+          <t>+23.30%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.44</v>
+        <v>4.249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2747,24 +2747,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0744%</t>
+          <t>0.0888%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.8735%</t>
+          <t>4.8014%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2795,26 +2795,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,042,601.48</t>
+          <t>¥1,049,086.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+42,601.48</t>
+          <t>¥+49,086.38</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+92.91%</t>
+          <t>+103.47%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.292</v>
+        <v>6.952</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2823,24 +2823,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2809%</t>
+          <t>0.3022%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10.9356%</t>
+          <t>10.6692%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2871,26 +2871,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,007,811.62</t>
+          <t>¥1,011,061.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+7,811.62</t>
+          <t>¥+11,061.62</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+13.04%</t>
+          <t>+17.71%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.849</v>
+        <v>5.152</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2899,24 +2899,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0521%</t>
+          <t>0.0690%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.8938%</t>
+          <t>2.9884%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2947,26 +2947,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,000,596.60</t>
+          <t>¥1,001,327.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+596.60</t>
+          <t>¥+1,327.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-2.063</v>
+        <v>0.207</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2975,24 +2975,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0040%</t>
+          <t>0.0083%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.4737%</t>
+          <t>0.5298%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -3023,26 +3023,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,000,663.50</t>
+          <t>¥1,001,421.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+663.50</t>
+          <t>¥+1,421.90</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-1.82</v>
+        <v>0.484</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0044%</t>
+          <t>0.0089%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.4752%</t>
+          <t>0.5356%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
